--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -958,7 +958,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.2.0}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>
